--- a/docs/handover/05_PoC_데이터_자산_목록.xlsx
+++ b/docs/handover/05_PoC_데이터_자산_목록.xlsx
@@ -913,7 +913,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>기후(12개 산지 기상 — ERA5-Land, 엘니뇨 지수, 산불)</t>
+          <t>기후(23개 산지 기상 — ERA5-Land 관측 + 15일 예보, 엘니뇨 지수, 산불)</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>12지역 × 8변수(설계값 약 22만 행) — 저장소 미보관</t>
+          <t>23지역(대두 19·팜유 4) × 8변수(설계값) + 예보 5변수 — 저장소 미보관</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>지역 축 분리 · 엘니뇨 지수 오독 정정(2026-08-16) · 증분 수집</t>
+          <t>지역 축 분리 · 엘니뇨 지수 오독 정정(2026-08-16) · 증분 수집 · 좌표 23곳 검증 완료(2026-09-13)</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>엔티티 191 · 관계 61종 · 인과 엣지 24(검증 10·후보 14)</t>
+          <t>엔티티 214 · 관계 61종 · 인과 엣지 24(검증 10·후보 14)</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">

--- a/docs/handover/05_PoC_데이터_자산_목록.xlsx
+++ b/docs/handover/05_PoC_데이터_자산_목록.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위_InOut" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="후속_단계" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검증_실적" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신뢰_지표" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -134,7 +135,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -177,6 +178,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1199,7 +1203,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="8">
       <c r="A20" s="12" t="inlineStr">
         <is>
@@ -1233,7 +1236,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="8">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -1588,7 +1590,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="8">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -1903,7 +1904,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="8">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="7" min="1" max="1"/>
@@ -2068,9 +2068,43 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>신뢰도 지표 2단계 체계(2026-09-14)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>1차(과거) 5종·2차(실시간) 6종 + 실발행 경보 원장 — 브리프 '보고서 신뢰도' 블록·월별 부록에 표시. 첫 산출: 순위 안정성 0.75, 참고 범위 포함률 5/20/60일 75/72/72%, 비정형 도달률 90%</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py · reports/market/g1_reliability_2026-09-14.md · 시트 '신뢰_지표'</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="15" customHeight="1" s="8">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2단계 시범판 실현성(2026-09-14)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>기준선 백테스트 80% 범위 포함률 5/20/60일 78/74/62% · 실시간 검증 12-03 첫 대조·2027-09 통계 의미 → 동결 유지</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>docs/research_desk/2026-09/g2_preview_feasibility_2026_09_14.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>출처: 05_PoC_범위_정의서.md §6 — 결과 정확도는 수치로 주장하지 않음(과정 무결성 4계층 기준)</t>
         </is>
@@ -2081,4 +2115,376 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="8" min="1" max="1"/>
+    <col width="24" customWidth="1" style="8" min="2" max="2"/>
+    <col width="46" customWidth="1" style="8" min="3" max="3"/>
+    <col width="34" customWidth="1" style="8" min="4" max="4"/>
+    <col width="26" customWidth="1" style="8" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>정의</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>첫 산출값(2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>판독</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1차(과거)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>변인 순위 안정성</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>확장 폴드 5구간 간 순위 상관·부호 일치</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>순위 상관 0.75 · 부호 일치 97.5%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>표본이 더해져도 같은 변인이 남음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1차(과거)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>인과 검정 재현성</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>전체 창 유의 관계의 부분 창 지속률</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>유의 2/10 · 지속률 1.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>정본 입력에서 재산출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1차(과거)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>경보 규칙 소급 성적</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>경보 뒤 5/20/60일 변동이 평소 이하인 비율(오경보 근사)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>해상운임 49/46/39%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>실발행 아님 — 소급 합성</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1차(과거)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>참고 범위 폭 진단</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>참고 범위가 실측을 담은 비율·폭(명목 80%)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5/20/60일 75/72/72%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>확률 주장 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1차(과거)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>유사 시기 참조 분별력</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>조건부 분포 폭 / 무조건부 폭</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.99~1.01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>정본 입력에서 재산출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2차(실시간)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>입력 정확도</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>정산가 교차검증 상대오차</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>중앙값 0.1003% · 상위 1% 1.34%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>롤링 250일 상시화 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2차(실시간)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>시점 정확도</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>정합 위반·개정 미보존 지표 수</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>위반 0 · 미보존 94/438</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>면책 자동 삽입</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2차(실시간)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>경보 정합성</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>경보판 = 서명 기록</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1 = 1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>불일치 시 발행 결함</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2차(실시간)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>발행 무결성</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>서명 기록 판정 분포·연속 통과</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16일 · 연속 5회</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>오염 이력 병기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2차(실시간)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>수집 채널 실적</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>비정형 도달률·채널 승자</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>90% · 23지표</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>첫 실행 로그 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2차(실시간)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>데이터 유형별 규칙 재검증</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5유형 발표 규칙의 실시간 성립</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>정합 4 · 대기 1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>매 산출 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2차(실시간)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>실발행 경보 원장</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>성숙 8회 이상부터 사후 성적</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2건 · 성숙 0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-09-14 개설</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/handover/05_PoC_데이터_자산_목록.xlsx
+++ b/docs/handover/05_PoC_데이터_자산_목록.xlsx
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>매 영업일 아침(한국시간 07~08시, 예정 04:17에서 실행 지연 흡수) 자동 발행. 핵심 변인·경보·과거 비슷한 시기·공급 경로·해상 위험·주요 지표·지정학 동향·뉴스·일정의 9블록(지정학 동향은 2026-09-25 신설)</t>
+          <t>매 영업일 아침(한국시간 07~08시, 예정 04:17에서 실행 지연 흡수) 자동 발행. 한눈 요약·가격 추세와 핵심 변인·경보·과거 비슷한 시기·공급 경로와 해상 위험·주요 지표·지정학 동향·뉴스·일정의 9블록(지정학 동향은 2026-09-25 신설)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2716,7 +2716,7 @@
     <col width="41.6" customWidth="1" min="2" max="2"/>
     <col width="50.40000000000001" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="41.6" customWidth="1" min="5" max="5"/>
+    <col width="49.3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>용어·인과 사전에서 키워드와 인과 경로를 파생, 창 14일, 지정학 기사 포함, 변인마다 '연결 근거' 한 줄(경로 미등재는 "상관 기반 참고")</t>
+          <t>용어·인과 사전에서 키워드와 사전 등재 경로를 파생, 창 14일, 지정학 기사 포함, 변인마다 '연결 근거' 한 줄(사전의 검증 상태 표기 — 당일 인과 식별이 아님 · 경로 미등재는 "상관 기반 참고")</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>사례별 관련 변수를 등재해 날짜 겹침 AND 인과 관련일 때만 배지, 변수→대두유 연결 설명 추가</t>
+          <t>사례별 관련 변수를 등재해 날짜 겹침 AND 관련 변수 등재일 때만 배지(관련성 필터 — 인과 증명 아님), 변수→대두유 연결 설명(사전 등재 경로) 추가</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>수집 단계에서 기사별 한국어 헤드라인 생성(정확도 우선 외부 언어모델·캐시·일 상한 60건), 브리프는 헤드라인 + 원제 보조줄</t>
+          <t>수집 단계에서 기사별 한국어 헤드라인 생성(정확도 우선 외부 언어모델·캐시로 중복 호출 최소화·일 상한 60건 초과분과 실패분은 원제 유지), 브리프는 헤드라인 + 원제 보조줄</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>✅ 2026-09-27 반영 · 첫 실데이터는 다음 자동 실행부터</t>
+          <t>🔁 2026-09-27 적용 · 실판정은 자동 실행 결과로(§10 하단 기록)</t>
         </is>
       </c>
     </row>

--- a/docs/handover/05_PoC_데이터_자산_목록.xlsx
+++ b/docs/handover/05_PoC_데이터_자산_목록.xlsx
@@ -2716,7 +2716,7 @@
     <col width="41.6" customWidth="1" min="2" max="2"/>
     <col width="50.40000000000001" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="49.3" customWidth="1" min="5" max="5"/>
+    <col width="54.8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>🔁 2026-09-27 적용 · 실판정은 자동 실행 결과로(§10 하단 기록)</t>
+          <t>✅ 2026-09-27 실판정 — 자동 실행 #115에서 11건 생성·브리프 반영 확인</t>
         </is>
       </c>
     </row>
